--- a/Steam_Games.xlsx
+++ b/Steam_Games.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CJ\Documents\My Projects\My Skill Development\game-achievement-data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4ADEB1EC-BA1D-41D0-A6C9-4F2B13203FCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D253A60-2427-42FB-9280-25184DC0A834}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>ID</t>
   </si>
@@ -54,6 +54,9 @@
   </si>
   <si>
     <t>Black Myth Wukong</t>
+  </si>
+  <si>
+    <t>game_link</t>
   </si>
 </sst>
 </file>
@@ -95,7 +98,11 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -109,14 +116,17 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{507F0839-0555-426B-B7DB-068B4BAF2678}" name="Table1" displayName="Table1" ref="A1:C4" totalsRowShown="0">
-  <autoFilter ref="A1:C4" xr:uid="{507F0839-0555-426B-B7DB-068B4BAF2678}"/>
-  <tableColumns count="3">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{507F0839-0555-426B-B7DB-068B4BAF2678}" name="Table1" displayName="Table1" ref="A1:D4" totalsRowShown="0">
+  <autoFilter ref="A1:D4" xr:uid="{507F0839-0555-426B-B7DB-068B4BAF2678}"/>
+  <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{3E161485-89FB-41E6-A63E-4664D0B0ECB0}" name="ID">
       <calculatedColumnFormula>ROW()-1</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="2" xr3:uid="{007859EE-C1EE-44C6-BFAC-1E67740E87F2}" name="Game"/>
     <tableColumn id="3" xr3:uid="{C37BA298-9796-40A0-90DB-956803912E0C}" name="game_id"/>
+    <tableColumn id="4" xr3:uid="{A71223AC-FD24-4499-A224-DD876F6C628B}" name="game_link" dataDxfId="0">
+      <calculatedColumnFormula>"https://steamdb.info/app/"&amp;Table1[[#This Row],[game_id]]&amp;"/stats/"</calculatedColumnFormula>
+    </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -385,10 +395,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -398,8 +408,11 @@
       <c r="C1" t="s">
         <v>4</v>
       </c>
+      <c r="D1" t="s">
+        <v>6</v>
+      </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2">
         <f>ROW()-1</f>
         <v>1</v>
@@ -410,8 +423,12 @@
       <c r="C2">
         <v>2358720</v>
       </c>
+      <c r="D2" t="str">
+        <f>"https://steamdb.info/app/"&amp;Table1[[#This Row],[game_id]]&amp;"/stats/"</f>
+        <v>https://steamdb.info/app/2358720/stats/</v>
+      </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3">
         <f>ROW()-1</f>
         <v>2</v>
@@ -422,8 +439,12 @@
       <c r="C3">
         <v>1627720</v>
       </c>
+      <c r="D3" t="str">
+        <f>"https://steamdb.info/app/"&amp;Table1[[#This Row],[game_id]]&amp;"/stats/"</f>
+        <v>https://steamdb.info/app/1627720/stats/</v>
+      </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4">
         <f>ROW()-1</f>
         <v>3</v>
@@ -433,6 +454,10 @@
       </c>
       <c r="C4">
         <v>1245620</v>
+      </c>
+      <c r="D4" t="str">
+        <f>"https://steamdb.info/app/"&amp;Table1[[#This Row],[game_id]]&amp;"/stats/"</f>
+        <v>https://steamdb.info/app/1245620/stats/</v>
       </c>
     </row>
   </sheetData>

--- a/Steam_Games.xlsx
+++ b/Steam_Games.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CJ\Documents\My Projects\My Skill Development\game-achievement-data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D253A60-2427-42FB-9280-25184DC0A834}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BFA3DF4-4193-4558-BADC-CB9590DB6AC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="768" yWindow="768" windowWidth="13284" windowHeight="13416" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t>ID</t>
   </si>
@@ -57,6 +57,33 @@
   </si>
   <si>
     <t>game_link</t>
+  </si>
+  <si>
+    <t>Sekiro: Shadows Die Twice</t>
+  </si>
+  <si>
+    <t>Elden Ring Nightreign</t>
+  </si>
+  <si>
+    <t>Hollow Knight Silksong</t>
+  </si>
+  <si>
+    <t>Hollow Knight</t>
+  </si>
+  <si>
+    <t>Sifu</t>
+  </si>
+  <si>
+    <t>Hades</t>
+  </si>
+  <si>
+    <t>Hades II</t>
+  </si>
+  <si>
+    <t>Clair Obscur: Expedition 33</t>
+  </si>
+  <si>
+    <t>Cuphead</t>
   </si>
 </sst>
 </file>
@@ -92,8 +119,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -116,8 +144,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{507F0839-0555-426B-B7DB-068B4BAF2678}" name="Table1" displayName="Table1" ref="A1:D4" totalsRowShown="0">
-  <autoFilter ref="A1:D4" xr:uid="{507F0839-0555-426B-B7DB-068B4BAF2678}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{507F0839-0555-426B-B7DB-068B4BAF2678}" name="Table1" displayName="Table1" ref="A1:D13" totalsRowShown="0">
+  <autoFilter ref="A1:D13" xr:uid="{507F0839-0555-426B-B7DB-068B4BAF2678}"/>
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{3E161485-89FB-41E6-A63E-4664D0B0ECB0}" name="ID">
       <calculatedColumnFormula>ROW()-1</calculatedColumnFormula>
@@ -395,7 +423,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
@@ -414,7 +442,7 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2">
-        <f>ROW()-1</f>
+        <f t="shared" ref="A2:A12" si="0">ROW()-1</f>
         <v>1</v>
       </c>
       <c r="B2" t="s">
@@ -430,7 +458,7 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3">
-        <f>ROW()-1</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="B3" t="s">
@@ -446,7 +474,7 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4">
-        <f>ROW()-1</f>
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="B4" t="s">
@@ -458,6 +486,150 @@
       <c r="D4" t="str">
         <f>"https://steamdb.info/app/"&amp;Table1[[#This Row],[game_id]]&amp;"/stats/"</f>
         <v>https://steamdb.info/app/1245620/stats/</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5">
+        <v>814380</v>
+      </c>
+      <c r="D5" t="str">
+        <f>"https://steamdb.info/app/"&amp;Table1[[#This Row],[game_id]]&amp;"/stats/"</f>
+        <v>https://steamdb.info/app/814380/stats/</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6">
+        <v>2622380</v>
+      </c>
+      <c r="D6" t="str">
+        <f>"https://steamdb.info/app/"&amp;Table1[[#This Row],[game_id]]&amp;"/stats/"</f>
+        <v>https://steamdb.info/app/2622380/stats/</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7">
+        <v>1030300</v>
+      </c>
+      <c r="D7" t="str">
+        <f>"https://steamdb.info/app/"&amp;Table1[[#This Row],[game_id]]&amp;"/stats/"</f>
+        <v>https://steamdb.info/app/1030300/stats/</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8">
+        <v>367520</v>
+      </c>
+      <c r="D8" t="str">
+        <f>"https://steamdb.info/app/"&amp;Table1[[#This Row],[game_id]]&amp;"/stats/"</f>
+        <v>https://steamdb.info/app/367520/stats/</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9">
+        <v>2138710</v>
+      </c>
+      <c r="D9" t="str">
+        <f>"https://steamdb.info/app/"&amp;Table1[[#This Row],[game_id]]&amp;"/stats/"</f>
+        <v>https://steamdb.info/app/2138710/stats/</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10">
+        <v>1145360</v>
+      </c>
+      <c r="D10" t="str">
+        <f>"https://steamdb.info/app/"&amp;Table1[[#This Row],[game_id]]&amp;"/stats/"</f>
+        <v>https://steamdb.info/app/1145360/stats/</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>13</v>
+      </c>
+      <c r="C11">
+        <v>1145350</v>
+      </c>
+      <c r="D11" t="str">
+        <f>"https://steamdb.info/app/"&amp;Table1[[#This Row],[game_id]]&amp;"/stats/"</f>
+        <v>https://steamdb.info/app/1145350/stats/</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C12">
+        <v>1903340</v>
+      </c>
+      <c r="D12" t="str">
+        <f>"https://steamdb.info/app/"&amp;Table1[[#This Row],[game_id]]&amp;"/stats/"</f>
+        <v>https://steamdb.info/app/1903340/stats/</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A13">
+        <f>ROW()-1</f>
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>15</v>
+      </c>
+      <c r="C13">
+        <v>268910</v>
+      </c>
+      <c r="D13" s="1" t="str">
+        <f>"https://steamdb.info/app/"&amp;Table1[[#This Row],[game_id]]&amp;"/stats/"</f>
+        <v>https://steamdb.info/app/268910/stats/</v>
       </c>
     </row>
   </sheetData>
